--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="22.83203125" customWidth="1"/>
@@ -438,7 +438,7 @@
         <v>10001</v>
       </c>
       <c r="B2" t="str">
-        <v>HuiXin</v>
+        <v>Hui Xin</v>
       </c>
       <c r="C2" t="str">
         <v>Main User</v>
@@ -453,7 +453,7 @@
         <v>2026-09-19T17:31:08.516Z</v>
       </c>
       <c r="G2" t="str">
-        <v>2026-09-19T17:31:08.516Z</v>
+        <v>2026-09-26T01:50:30.153Z</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>10002</v>
       </c>
       <c r="B3" t="str">
-        <v>Ali</v>
+        <v>Lennon</v>
       </c>
       <c r="C3" t="str">
         <v>Member</v>
@@ -476,7 +476,7 @@
         <v>2026-09-19T17:31:08.516Z</v>
       </c>
       <c r="G3" t="str">
-        <v>2026-09-19T17:31:08.516Z</v>
+        <v>2026-09-26T01:50:30.153Z</v>
       </c>
     </row>
     <row r="4">
@@ -484,7 +484,7 @@
         <v>10003</v>
       </c>
       <c r="B4" t="str">
-        <v>Abu</v>
+        <v>Kwai Mee</v>
       </c>
       <c r="C4" t="str">
         <v>Member</v>
@@ -499,7 +499,7 @@
         <v>2026-09-19T17:31:08.516Z</v>
       </c>
       <c r="G4" t="str">
-        <v>2026-09-19T17:31:08.516Z</v>
+        <v>2026-09-26T01:50:30.153Z</v>
       </c>
     </row>
     <row r="5">
@@ -507,7 +507,7 @@
         <v>10004</v>
       </c>
       <c r="B5" t="str">
-        <v>Ahmad</v>
+        <v>Hui Ping</v>
       </c>
       <c r="C5" t="str">
         <v>Member</v>
@@ -522,19 +522,65 @@
         <v>2026-09-19T17:31:08.516Z</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-09-19T17:31:08.516Z</v>
+        <v>2026-09-26T01:50:30.153Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>10005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hon Ling</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D6" t="str">
+        <v>f3cfb42b1666273dedf4e71819c7f59bb612f5d76c3dec0c546db0ccff2b982b</v>
+      </c>
+      <c r="E6" t="str">
+        <v>9ebd495a8e890964e477166d9dab9c67</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-09-26T03:25:58.507Z</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-09-26T03:25:58.507Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>10006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Jai Long</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D7" t="str">
+        <v>c2ff9188f1adca024ce0a5076c5d75ded7b3c5e29789b150971ddab586436d7c</v>
+      </c>
+      <c r="E7" t="str">
+        <v>780d53eedfc42390b4cbd7e4426aa36e</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-09-26T03:26:05.187Z</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-09-26T03:26:05.187Z</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -597,25 +643,25 @@
         <v>10001</v>
       </c>
       <c r="B2" t="str">
-        <v>HuiXin</v>
+        <v>Hui Xin</v>
       </c>
       <c r="C2" t="str">
         <v>Main User</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>100.5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>28.5</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -624,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L2" t="str">
-        <v>Owed SGD27.00 (To Receive)</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="M2" t="str">
-        <v>Receives SGD27.00 from group</v>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="3">
@@ -638,25 +684,25 @@
         <v>10002</v>
       </c>
       <c r="B3" t="str">
-        <v>Ali</v>
+        <v>Lennon</v>
       </c>
       <c r="C3" t="str">
         <v>Member</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -665,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L3" t="str">
-        <v>Owed SGD40.00 (To Receive)</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="M3" t="str">
-        <v>Receives SGD40.00 from group</v>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="4">
@@ -679,25 +725,25 @@
         <v>10003</v>
       </c>
       <c r="B4" t="str">
-        <v>Abu</v>
+        <v>Kwai Mee</v>
       </c>
       <c r="C4" t="str">
         <v>Member</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -706,13 +752,13 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="L4" t="str">
-        <v>Owes SGD22.00 (To Pay)</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="M4" t="str">
-        <v>Pays SGD22.00 to group</v>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="5">
@@ -720,7 +766,7 @@
         <v>10004</v>
       </c>
       <c r="B5" t="str">
-        <v>Ahmad</v>
+        <v>Hui Ping</v>
       </c>
       <c r="C5" t="str">
         <v>Member</v>
@@ -738,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -747,25 +793,107 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="L5" t="str">
-        <v>Owes SGD45.00 (To Pay)</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="M5" t="str">
-        <v>Pays SGD45.00 to group</v>
+        <v>All settled with group</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>10005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Hon Ling</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="M6" t="str">
+        <v>All settled with group</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>10006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Jai Long</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Member</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="M7" t="str">
+        <v>All settled with group</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C148"/>
   <cols>
     <col min="1" max="1" width="48.83203125" customWidth="1"/>
     <col min="2" max="2" width="40.83203125" customWidth="1"/>
@@ -799,10 +927,10 @@
         <v>Group Total Spending (All Time)</v>
       </c>
       <c r="B3" t="str">
-        <v>SGD195.50</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C3" t="str">
-        <v>5 total expense transactions recorded</v>
+        <v>0 total expense transactions recorded</v>
       </c>
     </row>
     <row r="4">
@@ -810,7 +938,7 @@
         <v>Total Shared Group Expenses</v>
       </c>
       <c r="B4" t="str">
-        <v>SGD167.00</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C4" t="str">
         <v>Split among participating group members</v>
@@ -821,7 +949,7 @@
         <v>Total Personal Spending (My Stuff)</v>
       </c>
       <c r="B5" t="str">
-        <v>SGD28.50</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C5" t="str">
         <v>Individual private expenses</v>
@@ -862,318 +990,318 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Total Registered Members</v>
+        <v>Base Currency Code</v>
       </c>
       <c r="B9" t="str">
-        <v>4</v>
+        <v>SGD</v>
       </c>
       <c r="C9" t="str">
-        <v>5-digit numeric IDs assigned</v>
+        <v>Base storage currency code</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Last Updated At</v>
+        <v>Base Currency Symbol</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-09-19T17:38:25.490Z</v>
+        <v>SGD</v>
       </c>
       <c r="C10" t="str">
-        <v>UTC Timestamp</v>
+        <v>Base storage currency symbol</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Storage Engine</v>
+        <v>User Currencies JSON</v>
       </c>
       <c r="B11" t="str">
-        <v>Excel (.xlsx) Database File</v>
+        <v>{"10001":"SGD"}</v>
       </c>
       <c r="C11" t="str">
-        <v>Direct spreadsheet persistence</v>
+        <v>Per-member default currency preferences</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Total Registered Members</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="C12" t="str">
-        <v/>
+        <v>5-digit numeric IDs assigned</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>=== INDEPENDENT FINANCIAL SUMMARY FOR EACH MEMBER ===</v>
+        <v>Last Updated At</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>2026-09-26T04:19:11.549Z</v>
       </c>
       <c r="C13" t="str">
-        <v/>
+        <v>UTC Timestamp</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Member: 10001 - HuiXin (Main User)</v>
+        <v>Storage Engine</v>
       </c>
       <c r="B14" t="str">
-        <v>Net Balance: +SGD27.00</v>
+        <v>Excel (.xlsx) Database File</v>
       </c>
       <c r="C14" t="str">
-        <v>Receives SGD27.00 from group</v>
+        <v>Direct spreadsheet persistence</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Member: 10002 - Ali (Member)</v>
+        <v/>
       </c>
       <c r="B15" t="str">
-        <v>Net Balance: +SGD40.00</v>
+        <v/>
       </c>
       <c r="C15" t="str">
-        <v>Receives SGD40.00 from group</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Member: 10003 - Abu (Member)</v>
+        <v>=== INDEPENDENT FINANCIAL SUMMARY FOR EACH MEMBER ===</v>
       </c>
       <c r="B16" t="str">
-        <v>Net Balance: SGD-22.00</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>Pays SGD22.00 to group</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Member: 10004 - Ahmad (Member)</v>
+        <v>Member: 10001 - Hui Xin (Main User)</v>
       </c>
       <c r="B17" t="str">
-        <v>Net Balance: SGD-45.00</v>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C17" t="str">
-        <v>Pays SGD45.00 to group</v>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Member: 10002 - Lennon (Member)</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10001 - HuiXin (Main User) &lt;&lt;&lt;</v>
+        <v>Member: 10003 - Kwai Mee (Member)</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C19" t="str">
-        <v/>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">  Member ID</v>
+        <v>Member: 10004 - Hui Ping (Member)</v>
       </c>
       <c r="B20" t="str">
-        <v>10001</v>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C20" t="str">
-        <v>Unique 5-digit ID</v>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">  Member Name</v>
+        <v>Member: 10005 - Hon Ling (Member)</v>
       </c>
       <c r="B21" t="str">
-        <v>HuiXin</v>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C21" t="str">
-        <v/>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">  Account Role</v>
+        <v>Member: 10006 - Jai Long (Member)</v>
       </c>
       <c r="B22" t="str">
-        <v>Main User</v>
+        <v>Net Balance: +SGD0.00</v>
       </c>
       <c r="C22" t="str">
-        <v/>
+        <v>All settled with group</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+        <v/>
       </c>
       <c r="B23" t="str">
-        <v>3</v>
+        <v/>
       </c>
       <c r="C23" t="str">
-        <v>Transactions paid out-of-pocket</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10001 - Hui Xin (Main User) &lt;&lt;&lt;</v>
       </c>
       <c r="B24" t="str">
-        <v>SGD100.50</v>
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v>Shared + Personal combined</v>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v xml:space="preserve">  Personal Items Paid</v>
+        <v xml:space="preserve">  Member ID</v>
       </c>
       <c r="B25" t="str">
-        <v>SGD28.50</v>
+        <v>10001</v>
       </c>
       <c r="C25" t="str">
-        <v>100% individual spending</v>
+        <v>Unique 5-digit ID</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v xml:space="preserve">  Shared Items Paid</v>
+        <v xml:space="preserve">  Member Name</v>
       </c>
       <c r="B26" t="str">
-        <v>SGD72.00</v>
+        <v>Hui Xin</v>
       </c>
       <c r="C26" t="str">
-        <v>Group expenses paid by this member</v>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+        <v xml:space="preserve">  Account Role</v>
       </c>
       <c r="B27" t="str">
-        <v>SGD45.00</v>
+        <v>Main User</v>
       </c>
       <c r="C27" t="str">
-        <v>This member's calculated portion</v>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v xml:space="preserve">  Settlements Paid Out</v>
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
       </c>
       <c r="B28" t="str">
-        <v>SGD0.00</v>
+        <v>0</v>
       </c>
       <c r="C28" t="str">
-        <v>Repayments made to others</v>
+        <v>Transactions paid out-of-pocket</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">  Settlements Received</v>
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
       </c>
       <c r="B29" t="str">
         <v>SGD0.00</v>
       </c>
       <c r="C29" t="str">
-        <v>Repayments received from others</v>
+        <v>Shared + Personal combined</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">  Net Balance with Group</v>
+        <v xml:space="preserve">  Personal Items Paid</v>
       </c>
       <c r="B30" t="str">
-        <v>+SGD27.00</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C30" t="str">
-        <v>Positive: Group owes this member</v>
+        <v>100% individual spending</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">  Settlement Status</v>
+        <v xml:space="preserve">  Shared Items Paid</v>
       </c>
       <c r="B31" t="str">
-        <v>Owed SGD27.00 (To Receive)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>Group expenses paid by this member</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">  Action Required</v>
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
       </c>
       <c r="B32" t="str">
-        <v>Receives SGD27.00 from group</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C32" t="str">
-        <v/>
+        <v>This member's calculated portion</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+        <v xml:space="preserve">  Settlements Paid Out</v>
       </c>
       <c r="B33" t="str">
-        <v/>
+        <v>SGD0.00</v>
       </c>
       <c r="C33" t="str">
-        <v/>
+        <v>Repayments made to others</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v xml:space="preserve">    With Ali (10002)</v>
+        <v xml:space="preserve">  Settlements Received</v>
       </c>
       <c r="B34" t="str">
-        <v>Settled (SGD0.00)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C34" t="str">
-        <v>No outstanding balance</v>
+        <v>Repayments received from others</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">    With Abu (10003)</v>
+        <v xml:space="preserve">  Net Balance with Group</v>
       </c>
       <c r="B35" t="str">
-        <v>Owed SGD7.00 (To Receive)</v>
+        <v>+SGD0.00</v>
       </c>
       <c r="C35" t="str">
-        <v>Abu owes HuiXin SGD7.00</v>
+        <v>Positive: Group owes this member</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">    With Ahmad (10004)</v>
+        <v xml:space="preserve">  Settlement Status</v>
       </c>
       <c r="B36" t="str">
-        <v>Owed SGD20.00 (To Receive)</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C36" t="str">
-        <v>Ahmad owes HuiXin SGD20.00</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v xml:space="preserve">  Action Required</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>All settled with group</v>
       </c>
       <c r="C37" t="str">
         <v/>
@@ -1181,7 +1309,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10002 - Ali (Member) &lt;&lt;&lt;</v>
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -1192,208 +1320,208 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">  Member ID</v>
+        <v xml:space="preserve">    With Lennon (10002)</v>
       </c>
       <c r="B39" t="str">
-        <v>10002</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C39" t="str">
-        <v>Unique 5-digit ID</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">  Member Name</v>
+        <v xml:space="preserve">    With Kwai Mee (10003)</v>
       </c>
       <c r="B40" t="str">
-        <v>Ali</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">  Account Role</v>
+        <v xml:space="preserve">    With Hui Ping (10004)</v>
       </c>
       <c r="B41" t="str">
-        <v>Member</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C41" t="str">
-        <v/>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+        <v xml:space="preserve">    With Hon Ling (10005)</v>
       </c>
       <c r="B42" t="str">
-        <v>1</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C42" t="str">
-        <v>Transactions paid out-of-pocket</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+        <v xml:space="preserve">    With Jai Long (10006)</v>
       </c>
       <c r="B43" t="str">
-        <v>SGD80.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C43" t="str">
-        <v>Shared + Personal combined</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v xml:space="preserve">  Personal Items Paid</v>
+        <v/>
       </c>
       <c r="B44" t="str">
-        <v>SGD0.00</v>
+        <v/>
       </c>
       <c r="C44" t="str">
-        <v>100% individual spending</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v xml:space="preserve">  Shared Items Paid</v>
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10002 - Lennon (Member) &lt;&lt;&lt;</v>
       </c>
       <c r="B45" t="str">
-        <v>SGD80.00</v>
+        <v/>
       </c>
       <c r="C45" t="str">
-        <v>Group expenses paid by this member</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+        <v xml:space="preserve">  Member ID</v>
       </c>
       <c r="B46" t="str">
-        <v>SGD40.00</v>
+        <v>10002</v>
       </c>
       <c r="C46" t="str">
-        <v>This member's calculated portion</v>
+        <v>Unique 5-digit ID</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v xml:space="preserve">  Settlements Paid Out</v>
+        <v xml:space="preserve">  Member Name</v>
       </c>
       <c r="B47" t="str">
-        <v>SGD0.00</v>
+        <v>Lennon</v>
       </c>
       <c r="C47" t="str">
-        <v>Repayments made to others</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v xml:space="preserve">  Settlements Received</v>
+        <v xml:space="preserve">  Account Role</v>
       </c>
       <c r="B48" t="str">
-        <v>SGD0.00</v>
+        <v>Member</v>
       </c>
       <c r="C48" t="str">
-        <v>Repayments received from others</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v xml:space="preserve">  Net Balance with Group</v>
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
       </c>
       <c r="B49" t="str">
-        <v>+SGD40.00</v>
+        <v>0</v>
       </c>
       <c r="C49" t="str">
-        <v>Positive: Group owes this member</v>
+        <v>Transactions paid out-of-pocket</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v xml:space="preserve">  Settlement Status</v>
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
       </c>
       <c r="B50" t="str">
-        <v>Owed SGD40.00 (To Receive)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C50" t="str">
-        <v/>
+        <v>Shared + Personal combined</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v xml:space="preserve">  Action Required</v>
+        <v xml:space="preserve">  Personal Items Paid</v>
       </c>
       <c r="B51" t="str">
-        <v>Receives SGD40.00 from group</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C51" t="str">
-        <v/>
+        <v>100% individual spending</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+        <v xml:space="preserve">  Shared Items Paid</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>SGD0.00</v>
       </c>
       <c r="C52" t="str">
-        <v/>
+        <v>Group expenses paid by this member</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v xml:space="preserve">    With HuiXin (10001)</v>
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
       </c>
       <c r="B53" t="str">
-        <v>Settled (SGD0.00)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C53" t="str">
-        <v>No outstanding balance</v>
+        <v>This member's calculated portion</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v xml:space="preserve">    With Abu (10003)</v>
+        <v xml:space="preserve">  Settlements Paid Out</v>
       </c>
       <c r="B54" t="str">
-        <v>Owed SGD20.00 (To Receive)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C54" t="str">
-        <v>Abu owes Ali SGD20.00</v>
+        <v>Repayments made to others</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v xml:space="preserve">    With Ahmad (10004)</v>
+        <v xml:space="preserve">  Settlements Received</v>
       </c>
       <c r="B55" t="str">
-        <v>Owed SGD20.00 (To Receive)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C55" t="str">
-        <v>Ahmad owes Ali SGD20.00</v>
+        <v>Repayments received from others</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v xml:space="preserve">  Net Balance with Group</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>+SGD0.00</v>
       </c>
       <c r="C56" t="str">
-        <v/>
+        <v>Positive: Group owes this member</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10003 - Abu (Member) &lt;&lt;&lt;</v>
+        <v xml:space="preserve">  Settlement Status</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C57" t="str">
         <v/>
@@ -1401,21 +1529,21 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v xml:space="preserve">  Member ID</v>
+        <v xml:space="preserve">  Action Required</v>
       </c>
       <c r="B58" t="str">
-        <v>10003</v>
+        <v>All settled with group</v>
       </c>
       <c r="C58" t="str">
-        <v>Unique 5-digit ID</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v xml:space="preserve">  Member Name</v>
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
       </c>
       <c r="B59" t="str">
-        <v>Abu</v>
+        <v/>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1423,109 +1551,109 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v xml:space="preserve">  Account Role</v>
+        <v xml:space="preserve">    With Hui Xin (10001)</v>
       </c>
       <c r="B60" t="str">
-        <v>Member</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C60" t="str">
-        <v/>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+        <v xml:space="preserve">    With Kwai Mee (10003)</v>
       </c>
       <c r="B61" t="str">
-        <v>1</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C61" t="str">
-        <v>Transactions paid out-of-pocket</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+        <v xml:space="preserve">    With Hui Ping (10004)</v>
       </c>
       <c r="B62" t="str">
-        <v>SGD15.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C62" t="str">
-        <v>Shared + Personal combined</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v xml:space="preserve">  Personal Items Paid</v>
+        <v xml:space="preserve">    With Hon Ling (10005)</v>
       </c>
       <c r="B63" t="str">
-        <v>SGD0.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C63" t="str">
-        <v>100% individual spending</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">  Shared Items Paid</v>
+        <v xml:space="preserve">    With Jai Long (10006)</v>
       </c>
       <c r="B64" t="str">
-        <v>SGD15.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C64" t="str">
-        <v>Group expenses paid by this member</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+        <v/>
       </c>
       <c r="B65" t="str">
-        <v>SGD37.00</v>
+        <v/>
       </c>
       <c r="C65" t="str">
-        <v>This member's calculated portion</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v xml:space="preserve">  Settlements Paid Out</v>
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10003 - Kwai Mee (Member) &lt;&lt;&lt;</v>
       </c>
       <c r="B66" t="str">
-        <v>SGD0.00</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>Repayments made to others</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v xml:space="preserve">  Settlements Received</v>
+        <v xml:space="preserve">  Member ID</v>
       </c>
       <c r="B67" t="str">
-        <v>SGD0.00</v>
+        <v>10003</v>
       </c>
       <c r="C67" t="str">
-        <v>Repayments received from others</v>
+        <v>Unique 5-digit ID</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v xml:space="preserve">  Net Balance with Group</v>
+        <v xml:space="preserve">  Member Name</v>
       </c>
       <c r="B68" t="str">
-        <v>SGD-22.00</v>
+        <v>Kwai Mee</v>
       </c>
       <c r="C68" t="str">
-        <v>Negative: This member owes group</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v xml:space="preserve">  Settlement Status</v>
+        <v xml:space="preserve">  Account Role</v>
       </c>
       <c r="B69" t="str">
-        <v>Owes SGD22.00 (To Pay)</v>
+        <v>Member</v>
       </c>
       <c r="C69" t="str">
         <v/>
@@ -1533,98 +1661,98 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v xml:space="preserve">  Action Required</v>
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
       </c>
       <c r="B70" t="str">
-        <v>Pays SGD22.00 to group</v>
+        <v>0</v>
       </c>
       <c r="C70" t="str">
-        <v/>
+        <v>Transactions paid out-of-pocket</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>SGD0.00</v>
       </c>
       <c r="C71" t="str">
-        <v/>
+        <v>Shared + Personal combined</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v xml:space="preserve">    With HuiXin (10001)</v>
+        <v xml:space="preserve">  Personal Items Paid</v>
       </c>
       <c r="B72" t="str">
-        <v>Owes SGD7.00 (To Pay)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C72" t="str">
-        <v>Abu owes HuiXin SGD7.00</v>
+        <v>100% individual spending</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v xml:space="preserve">    With Ali (10002)</v>
+        <v xml:space="preserve">  Shared Items Paid</v>
       </c>
       <c r="B73" t="str">
-        <v>Owes SGD20.00 (To Pay)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C73" t="str">
-        <v>Abu owes Ali SGD20.00</v>
+        <v>Group expenses paid by this member</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v xml:space="preserve">    With Ahmad (10004)</v>
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
       </c>
       <c r="B74" t="str">
-        <v>Owed SGD5.00 (To Receive)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C74" t="str">
-        <v>Ahmad owes Abu SGD5.00</v>
+        <v>This member's calculated portion</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v xml:space="preserve">  Settlements Paid Out</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>SGD0.00</v>
       </c>
       <c r="C75" t="str">
-        <v/>
+        <v>Repayments made to others</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10004 - Ahmad (Member) &lt;&lt;&lt;</v>
+        <v xml:space="preserve">  Settlements Received</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>SGD0.00</v>
       </c>
       <c r="C76" t="str">
-        <v/>
+        <v>Repayments received from others</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v xml:space="preserve">  Member ID</v>
+        <v xml:space="preserve">  Net Balance with Group</v>
       </c>
       <c r="B77" t="str">
-        <v>10004</v>
+        <v>+SGD0.00</v>
       </c>
       <c r="C77" t="str">
-        <v>Unique 5-digit ID</v>
+        <v>Positive: Group owes this member</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v xml:space="preserve">  Member Name</v>
+        <v xml:space="preserve">  Settlement Status</v>
       </c>
       <c r="B78" t="str">
-        <v>Ahmad</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C78" t="str">
         <v/>
@@ -1632,10 +1760,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v xml:space="preserve">  Account Role</v>
+        <v xml:space="preserve">  Action Required</v>
       </c>
       <c r="B79" t="str">
-        <v>Member</v>
+        <v>All settled with group</v>
       </c>
       <c r="C79" t="str">
         <v/>
@@ -1643,109 +1771,109 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
       </c>
       <c r="B80" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="C80" t="str">
-        <v>Transactions paid out-of-pocket</v>
+        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+        <v xml:space="preserve">    With Hui Xin (10001)</v>
       </c>
       <c r="B81" t="str">
-        <v>SGD0.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C81" t="str">
-        <v>Shared + Personal combined</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v xml:space="preserve">  Personal Items Paid</v>
+        <v xml:space="preserve">    With Lennon (10002)</v>
       </c>
       <c r="B82" t="str">
-        <v>SGD0.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C82" t="str">
-        <v>100% individual spending</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v xml:space="preserve">  Shared Items Paid</v>
+        <v xml:space="preserve">    With Hui Ping (10004)</v>
       </c>
       <c r="B83" t="str">
-        <v>SGD0.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C83" t="str">
-        <v>Group expenses paid by this member</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+        <v xml:space="preserve">    With Hon Ling (10005)</v>
       </c>
       <c r="B84" t="str">
-        <v>SGD45.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C84" t="str">
-        <v>This member's calculated portion</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v xml:space="preserve">  Settlements Paid Out</v>
+        <v xml:space="preserve">    With Jai Long (10006)</v>
       </c>
       <c r="B85" t="str">
-        <v>SGD0.00</v>
+        <v>Settled (SGD0.00)</v>
       </c>
       <c r="C85" t="str">
-        <v>Repayments made to others</v>
+        <v>No outstanding balance</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v xml:space="preserve">  Settlements Received</v>
+        <v/>
       </c>
       <c r="B86" t="str">
-        <v>SGD0.00</v>
+        <v/>
       </c>
       <c r="C86" t="str">
-        <v>Repayments received from others</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v xml:space="preserve">  Net Balance with Group</v>
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10004 - Hui Ping (Member) &lt;&lt;&lt;</v>
       </c>
       <c r="B87" t="str">
-        <v>SGD-45.00</v>
+        <v/>
       </c>
       <c r="C87" t="str">
-        <v>Negative: This member owes group</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v xml:space="preserve">  Settlement Status</v>
+        <v xml:space="preserve">  Member ID</v>
       </c>
       <c r="B88" t="str">
-        <v>Owes SGD45.00 (To Pay)</v>
+        <v>10004</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>Unique 5-digit ID</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v xml:space="preserve">  Action Required</v>
+        <v xml:space="preserve">  Member Name</v>
       </c>
       <c r="B89" t="str">
-        <v>Pays SGD45.00 to group</v>
+        <v>Hui Ping</v>
       </c>
       <c r="C89" t="str">
         <v/>
@@ -1753,10 +1881,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+        <v xml:space="preserve">  Account Role</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Member</v>
       </c>
       <c r="C90" t="str">
         <v/>
@@ -1764,40 +1892,645 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v xml:space="preserve">    With HuiXin (10001)</v>
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
       </c>
       <c r="B91" t="str">
-        <v>Owes SGD20.00 (To Pay)</v>
+        <v>0</v>
       </c>
       <c r="C91" t="str">
-        <v>Ahmad owes HuiXin SGD20.00</v>
+        <v>Transactions paid out-of-pocket</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v xml:space="preserve">    With Ali (10002)</v>
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
       </c>
       <c r="B92" t="str">
-        <v>Owes SGD20.00 (To Pay)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C92" t="str">
-        <v>Ahmad owes Ali SGD20.00</v>
+        <v>Shared + Personal combined</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v xml:space="preserve">    With Abu (10003)</v>
+        <v xml:space="preserve">  Personal Items Paid</v>
       </c>
       <c r="B93" t="str">
-        <v>Owes SGD5.00 (To Pay)</v>
+        <v>SGD0.00</v>
       </c>
       <c r="C93" t="str">
-        <v>Ahmad owes Abu SGD5.00</v>
+        <v>100% individual spending</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v xml:space="preserve">  Shared Items Paid</v>
+      </c>
+      <c r="B94" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Group expenses paid by this member</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+      </c>
+      <c r="B95" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C95" t="str">
+        <v>This member's calculated portion</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v xml:space="preserve">  Settlements Paid Out</v>
+      </c>
+      <c r="B96" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Repayments made to others</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v xml:space="preserve">  Settlements Received</v>
+      </c>
+      <c r="B97" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Repayments received from others</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v xml:space="preserve">  Net Balance with Group</v>
+      </c>
+      <c r="B98" t="str">
+        <v>+SGD0.00</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Positive: Group owes this member</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v xml:space="preserve">  Settlement Status</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v xml:space="preserve">  Action Required</v>
+      </c>
+      <c r="B100" t="str">
+        <v>All settled with group</v>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v xml:space="preserve">    With Hui Xin (10001)</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C102" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v xml:space="preserve">    With Lennon (10002)</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C103" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v xml:space="preserve">    With Kwai Mee (10003)</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C104" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v xml:space="preserve">    With Hon Ling (10005)</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C105" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v xml:space="preserve">    With Jai Long (10006)</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C106" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v/>
+      </c>
+      <c r="B107" t="str">
+        <v/>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10005 - Hon Ling (Member) &lt;&lt;&lt;</v>
+      </c>
+      <c r="B108" t="str">
+        <v/>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v xml:space="preserve">  Member ID</v>
+      </c>
+      <c r="B109" t="str">
+        <v>10005</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Unique 5-digit ID</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v xml:space="preserve">  Member Name</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Hon Ling</v>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v xml:space="preserve">  Account Role</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Member</v>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+      </c>
+      <c r="B112" t="str">
+        <v>0</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Transactions paid out-of-pocket</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+      </c>
+      <c r="B113" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Shared + Personal combined</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v xml:space="preserve">  Personal Items Paid</v>
+      </c>
+      <c r="B114" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C114" t="str">
+        <v>100% individual spending</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v xml:space="preserve">  Shared Items Paid</v>
+      </c>
+      <c r="B115" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Group expenses paid by this member</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+      </c>
+      <c r="B116" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C116" t="str">
+        <v>This member's calculated portion</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v xml:space="preserve">  Settlements Paid Out</v>
+      </c>
+      <c r="B117" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Repayments made to others</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v xml:space="preserve">  Settlements Received</v>
+      </c>
+      <c r="B118" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Repayments received from others</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v xml:space="preserve">  Net Balance with Group</v>
+      </c>
+      <c r="B119" t="str">
+        <v>+SGD0.00</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Positive: Group owes this member</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v xml:space="preserve">  Settlement Status</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v xml:space="preserve">  Action Required</v>
+      </c>
+      <c r="B121" t="str">
+        <v>All settled with group</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+      </c>
+      <c r="B122" t="str">
+        <v/>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v xml:space="preserve">    With Hui Xin (10001)</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C123" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v xml:space="preserve">    With Lennon (10002)</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C124" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v xml:space="preserve">    With Kwai Mee (10003)</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C125" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v xml:space="preserve">    With Hui Ping (10004)</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C126" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v xml:space="preserve">    With Jai Long (10006)</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C127" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v/>
+      </c>
+      <c r="B128" t="str">
+        <v/>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>&gt;&gt;&gt; DETAILED SUMMARY: 10006 - Jai Long (Member) &lt;&lt;&lt;</v>
+      </c>
+      <c r="B129" t="str">
+        <v/>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v xml:space="preserve">  Member ID</v>
+      </c>
+      <c r="B130" t="str">
+        <v>10006</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Unique 5-digit ID</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v xml:space="preserve">  Member Name</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Jai Long</v>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v xml:space="preserve">  Account Role</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Member</v>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v xml:space="preserve">  Total Expenses Logged/Paid</v>
+      </c>
+      <c r="B133" t="str">
+        <v>0</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Transactions paid out-of-pocket</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v xml:space="preserve">  Total Amount Paid (All Time)</v>
+      </c>
+      <c r="B134" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Shared + Personal combined</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v xml:space="preserve">  Personal Items Paid</v>
+      </c>
+      <c r="B135" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C135" t="str">
+        <v>100% individual spending</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v xml:space="preserve">  Shared Items Paid</v>
+      </c>
+      <c r="B136" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Group expenses paid by this member</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v xml:space="preserve">  Fair Share of Shared (Consumed)</v>
+      </c>
+      <c r="B137" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C137" t="str">
+        <v>This member's calculated portion</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v xml:space="preserve">  Settlements Paid Out</v>
+      </c>
+      <c r="B138" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Repayments made to others</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v xml:space="preserve">  Settlements Received</v>
+      </c>
+      <c r="B139" t="str">
+        <v>SGD0.00</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Repayments received from others</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v xml:space="preserve">  Net Balance with Group</v>
+      </c>
+      <c r="B140" t="str">
+        <v>+SGD0.00</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Positive: Group owes this member</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v xml:space="preserve">  Settlement Status</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v xml:space="preserve">  Action Required</v>
+      </c>
+      <c r="B142" t="str">
+        <v>All settled with group</v>
+      </c>
+      <c r="C142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v xml:space="preserve">  --- Pairwise Debts with Each Member ---</v>
+      </c>
+      <c r="B143" t="str">
+        <v/>
+      </c>
+      <c r="C143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v xml:space="preserve">    With Hui Xin (10001)</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C144" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v xml:space="preserve">    With Lennon (10002)</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C145" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v xml:space="preserve">    With Kwai Mee (10003)</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C146" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v xml:space="preserve">    With Hui Ping (10004)</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C147" t="str">
+        <v>No outstanding balance</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v xml:space="preserve">    With Hon Ling (10005)</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Settled (SGD0.00)</v>
+      </c>
+      <c r="C148" t="str">
+        <v>No outstanding balance</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C148"/>
   </ignoredErrors>
 </worksheet>
 </file>